--- a/output_excel/17176206.xlsx
+++ b/output_excel/17176206.xlsx
@@ -562,16 +562,20 @@
           <t>V5-6</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>30.96m</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>30K | 30K | BT0 | (DCIM) | AV. | 37,5KVA | 3x336AN | 30K | Z | (DCIM) | 112,5KVA | 30K | 30K | AV. | 112,5KVA | CONEX. | 112,5KVA | 37,5KVA | 112,5KVA | (DCIM) | (DCIM) | 1x3x120(70)AX | CONEX. | 37,5KVA | (DCIM) | 112,5KVA | 30K | 112,5KVA | 30K | 3x336AN | 112,5KVA | 112,5KVA | 112,5KVA | CAMPO | 37,5KVA | 112,5KVA | CONEX. | 175ET005296879 | CONEX. | 30K | 400816F | 30K | ANCORAR | 30K | 112,5KVA | BF-A | 3x336AN | (DCIM) | CONEX. | 37,5KVA | 112,5KVA | (DCIM) | 37,5KVA | 112,5KVA | BT | 112,5KVA | 30K | ANCORAR | 112,5KVA | CORDOALHA | 112,5KVA | BF-A | 3x336AN | (DCIM) | 37,5KVA | BT | (DCIM) | 112,5KVA | (DCIM) | V5-6 | 37,5KVA | 112,5KVA | B1F | CABOS | (DCIM) | 1x2x4AC | PROJETO | 112,5KVA | FERRAGEM | P6 | 1x2x4AC | (DCIM) | 30K | BT0 | (DCIM) | (DCIM) | AV. | CORDOALHA | 112,5KVA | 112,5KVA | 112,5KVA | 30K | 112,5KVA | 30K | COMPARTILHANTES | MT | 30K | (DCIM)112,5KVA | (KL)</t>
+          <t>(DCIM) | 3 | (DCIM) | 7 | 7 | AV. | 6 | 1 | 1 | AV. | 112,5KVA | 0 | CAMPO | 0 | 3 | 112,5KVA | 8 | 3 | 0 | BF-A | ANCORAR | 2 | 6 | (DCIM) | 175ET005296879 | (DCIM) | 7 | CONEX. | (DCIM) | 1 | 3x336AN | 0 | 2 | ANCORAR | BF-A | 7 | 2 | 6 | 112,5KVA | (DCIM) | Z | 7 | 1 | (DCIM) | 1 | BT0 | 7 | 112,5KVA | 1x3x120(70)AX | 1 | 5 | 7 | (DCIM) | (DCIM) | 0 | CONEX. | 2 | 112,5KVA | 1 | CABOS | 0 | CONEX. | 4 | 7 | 3 | 4 | CONEX. | (DCIM) | (DCIM) | CONEX. | 2 | 1 | 3 | 1 | 2 | (DCIM)112,5KVA | CONEX. | CABOS | BT | 6 | (KL) | B1F | BT | MT | 1 | (DCIM) | 0 | 112,5KVA | CORDOALHA | (DCIM) | (DCIM) | 1RU6A | B1F | 0 | 1AF(1) | 112,5KVA | (DCIM) | 112,5KVA | 2 | 1RU6A | C12x1000,CE2 | (DCIM) | (KL) | 1RU6A | ANCORAR | 3x70AX(5AZN) | 112,5KVA | 112,5KVA | (DCIM) | 1 | (DCIM) | 4 | (KL) | (DCIM) | 3 | (DCIM) | 112,5KVA | 112,5KVA | BT | CABOS | (DCIM) | 5</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -612,7 +616,7 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>BT | (DCIM) | 3M | 30K | (DCIM) | 1x2x4AC | AV. | 1x2x4AC | BT | AV. | 1x3x120(70)AX | 30K | 30K | (DCIM) | 30K | 30K | ANCORAR | 30K | CONEX. | (DCIM) | 37,5KVA | ANCORAR | 3x336AN | CONEX. | 112,5KVA | 30K | (DCIM) | 400816F | Z | BF-A | 112,5KVA | ANCORAR | 1x2x4AC | 1x3x120(70)AX | 112,5KVA | CONEX. | P8 | BT0 | 112,5KVA | 30K | B1F | BT | (DCIM) | (KL) | 3x185AX(5AZN) | 112,5KVA | 112,5KVA | CONEX. | 1x3x120(70)AX | CAMINHÃO | 30K | CONEX. | 112,5KVA | CONEX. | 30K | (DCIM) | 112,5KVA | 112,5KVA | BT | 112,5KVA | NF | 112,5KVA | Z | 30K | 112,5KVA | CONEX. | 30K | 37,5KVA | 112,5KVA | B1F | 3x336AN | (DCIM) | 30K | 112,5KVA | 37,5KVA | 112,5KVA | 400816F | CONEX. | BT | 30K | (DCIM) | CONEX. | (DCIM) | ANCORAR | 112,5KVA | (DCIM) | (DCIM) | ANCORAR | 30M | 30K | 30K | 112,5KVA | 112,5KVA | 112,5KVA | (DCIM) | CONEX. | ANCORAR | 112,5KVA | CONEX. | CONEX. | 112,5KVA | 112,5KVA | Z | 30K | 112,5KVA | (KL) | CORDOALHA | AV. | 3x336AN | CAMINHÃO | 112,5KVA | V3-8 | 44M | CMB | 112,5KVA | BT | 30K | (DCIM) | ANCORAR | P31 | BT | CE2-3LF | AV. | C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | 112,5KVA | B1F | 112,5KVA | (DCIM) | B1F | (DCIM) | 30K | BT | 112,5KVA | 30K | 30K | AV. | 112,5KVA | 112,5KVA | (DCIM)</t>
+          <t>BT | (DCIM) | 3M | 3 | (DCIM) | 4 | AV. | 4 | BT | AV. | 1x3x120(70)AX | 0 | 0 | (DCIM) | 3 | 3 | ANCORAR | 3 | CONEX. | (DCIM) | 7 | 1RU6A | 3x336AN | CONEX. | 112,5KVA | 0 | (DCIM) | 8 | Z | BF-A | 112,5KVA | ANCORAR | 4 | 1x3x120(70)AX | 112,5KVA | CONEX. | BT0 | 112,5KVA | 0 | B1F | BT | (DCIM) | (KL) | 3x185AX(5AZN) | 1 | 5 | CONEX. | 1x3x120(70)AX | CAMINHÃO | 3 | CONEX. | 112,5KVA | CONEX.</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -653,7 +657,7 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>(DCIM) | (DCIM) | ANCORAR | (DCIM) | BF-A | P2 | (DCIM) | ANCORAR | 400816F | BF-A | 30K | 37,5KVA | 112,5KVA | 30K | P1-11 | 3x336AN | 37,5KVA | 112,5KVA | (DCIM) | 37,5KVA | 30K | 3x336AN | (DCIM) | 112,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 112,5KVA | CAMPO | .7 | 171 | 37,5KVA | .7 | 112,5KVA | 1x2x4AC | 112,5KVA | BT | 1x2x4AC | 112,5KVA | AVENIDA | 112,5KVA | DG | (DCIM) | B1F | (DCIM) | (DCIM) | 3x336AN | BT | CONEX. | (DCIM) | 30K | BT | 112,5KVA | 112,5KVA | Z | BT | ANCORAR | 112,5KVA | (DCIM) | 1x3x120(70)AX | 112,5KVA | 30K | 112,5KVA | B1F | CONEX. | YOSHIDA | (DCIM) | CORDOALHA | CE2-3LF | 30K | BF-A | CONEX. | 30K | IP | 3x185AX(5AZN) | 112,5KVA | 112,5KVA | CABOS | 1x3x120(70)AX | MT | CONEX. | (DCIM)112,5KVA | 400816F | CONEX. | 3x185AX(5AZN) | ANCORAR | CAMINHÃO | 112,5KVA | 30K | 112,5KVA | 112,5KVA | (DCIM) | 112,5KVA | (KL) | S44(2)112,5KVASMPI | 112,5KVA | YOSHIDA | 112,5KVA | (DCIM) | 112,5KVA | 112,5KVA | 112,5KVA | 30K</t>
+          <t>(DCIM) | (DCIM) | ANCORAR | BF-A | (DCIM) | (DCIM) | ANCORAR | 8 | BF-A | 3 | 7 | 1 | 3 | 6 | 1 | 7 | (DCIM) | 7 | 0 | 6 | (DCIM) | 2 | 7 | 112,5KVA | 2 | 1 | CAMPO | .7 | 171 | 7 | 112,5KVA | .7 | 4 | 1 | BT | 4 | 1 | AVENIDA | DG | 1 | (DCIM) | B1F | (DCIM) | 3x336AN | CONEX. | 0 | BT | (DCIM) | (DCIM) | BT | Z | 112,5KVA | BT | 112,5KVA | ANCORAR | 1x3x120(70)AX | 1 | 2 | (DCIM) | 112,5KVA | B1F | 3 | (DCIM) | 0 | CONEX. | CORDOALHA | CE2-3LF | YOSHIDA | CONEX. | IP | BF-A | 3x185AX(5AZN) | 3 | 112,5KVA | MT | 1 | 1x3x120(70)AX | (DCIM)112,5KVA | CABOS | CONEX. | 3x185AX(5AZN) | CONEX. | CAMINHÃO | 2 | 8 | 0 | ANCORAR | 1 | (DCIM) | 112,5KVA | (KL) | 5 | 2 | (DCIM) | 1 | 2 | S44(2)112,5KVASMPI | YOSHIDA | 5 | 112,5KVA | 112,5KVA | 1</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -702,7 +706,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>P6 | 112,5KVA | 112,5KVA | 112,5KVA | (DCIM) | 37,5KVA | ANCORAR | ANCORAR | 112,5KVA | 112,5KVA | 112,5KVA | 37,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 112,5KVA | 112,5KVA | CABOS | 3x336AN | CONEX. | (DCIM) | 37,5KVA | 1x2x4AC | (DCIM) | (DCIM) | 112,5KVA | 3x336AN | 175ET005296879 | 3x336AN | 1x2x4AC | 112,5KVA | 112,5KVA | 30K | 112,5KVA | 112,5KVA | 112,5KVA | (DCIM) | CAMPO | 112,5KVA | 30K | 30K | 30K | (KL) | 112,5KVA | DIVISA | (DCIM)112,5KVA | 400816F | BF-A | 112,5KVA | C12x1000,CE2 | CABOS | 112,5KVA | BF-A | BT | 3x336AN | ANCORAR | (DCIM) | (KL) | ANCORAR | (DCIM) | ANCORAR | 37,5KVA | (DCIM) | (DCIM) | 1x2x4AC | 112,5KVA | 1AF(1) | AV. | BIF | BIF | 30K | (DCIM) | S44(2)112,5KVASMPI | 112,5KVA | (KL) | 30K | (DCIM) | (DCIM) | CABOS | CONEX. | (DCIM) | 30K | (DCIM) | (DCIM) | 112,5KVA | 37,5KVA | AV. | C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | 30K | 1x3x120(70)AX | 30K | RAMAL | 1AF(1) | (DCIM) | (DCIM) | 37,5KVA | (DCIM) | 112,5KVA | 3x336AN | (KL) | Z | 30K | (DCIM) | (DCIM) | 112,5KVA | 112,5KVA | 112,5KVA | B1F | 112,5KVA | (DCIM) | 112,5KVA | (DCIM) | CAMPO | (DCIM) | (DCIM) | CONEX. | CONEX. | BT0 | (KL) | 30K | BCU | 112,5KVA</t>
+          <t>S44(2)112,5KVASMPI | (DCIM) | C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | RAMAL | 1 | BIF</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -751,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>P5 | S44(2)112,5KVASMPI | (DCIM) | 112,5KVA | 30K | AV. | (DCIM) | C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | 30K | 112,5KVA | 30K | 30K | AV. | 30K | CONEX. | 30K | 112,5KVA | (DCIM) | 1x3x120(70)AX | RAMAL | 3x336AN | 30K | Z | 37,5KVA | (DCIM) | 30K | II | (DCIM) | 112,5KVA | BT | P6 | CONEX. | 30K | 112,5KVA | CONEX. | 112,5KVA | 30K | BT | 112,5KVA | 112,5KVA | B1F | 30K | B1F | (DCIM) | (DCIM) | BIF | 37,5KVA | 112,5KVA | 1x3x120(70)AX | CONEX. | 112,5KVA | 112,5KVA | 112,5KVA | CONEX. | 175ET005296879 | 112,5KVA | CAMINHÃO | 112,5KVA | CONEX. | CONEX. | 37,5KVA | 30K | 30K | BT | 112,5KVA | 30K | (DCIM) | CONEX. | 30K | (DCIM) | 112,5KVA | (KL) | 37,5KVA | 112,5KVA | CS´S | 30K | 30K | 30K | 112,5KVA | AV. | Z | 112,5KVA | (DCIM) | 37,5KVA | 112,5KVA | 112,5KVA | 37,5KVA | CONEX. | 112,5KVA | 3x336AN | 37,5KVA | (DCIM) | 112,5KVA | CONEX. | CAMPO | 37,5KVA | 112,5KVA | ANCORAR | 30K | (DCIM) | CORDOALHA | 30K | 30K | 37,5KVA | 3x336AN | 112,5KVA | AV. | (DCIM) | 37,5KVA | BT | BT0 | 3x336AN | 112,5KVA | YOSHIDA | 30K</t>
+          <t>S44(2)112,5KVASMPI | C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | 1 | RAMAL | (DCIM) | 5 | 3 | AV. | 3</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
@@ -800,11 +804,11 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>P2 | P1-11 | BF-A | B1F | (DCIM) | (DCIM) | BT | (DCIM) | (DCIM) | (DCIM) | 112,5KVA | 112,5KVA | (DCIM) | BT | (DCIM) | ANCORAR | CONEX. | S44(2)112,5KVASMPI | ANCORAR | 30K | 30K | BF-A | (DCIM) | P31 | 564660 | YOSHIDA | BF-A | CONEX. | CONEX. | ANCORAR | 400816F | 112,5KVA | 112,5KVA | CORDOALHA | CABOS | 37,5KVA | NF | 400816F | C12X600112,5KVACE4112,5KVABF-A112,5KVASMTG112,5KVAL1(2)112,5KVAIP | 112,5KVA | 30K | 37,5KVA | 112,5KVA | 30K | 112,5KVA | 112,5KVA | ANCORAR | 112,5KVA | 30K | 30K | (DCIM) | CE2-3LF | 112,5KVA | 112,5KVA | 1x3x120(70)AX | 3x336AN | YOSHIDA | (DCIM) | 3x336AN | 112,5KVA | (DCIM) | CONEX. | B1F | 1AF(1) | 37,5KVA | 112,5KVA | 112,5KVA | 3x336AN | 30K | 37,5KVA | 112,5KVA | 46 | CAMPO | 3x185AX(5AZN) | ESTR. | 3x336AN | 1x3x120(70)AX | 112,5KVA | 30K | .7 | 112,5KVA | .7 | 112,5KVA | 112,5KVA | 37,5KVA | 1x2x4AC | 112,5KVA | 1x2x4AC | BT | 171 | CONEX. | Z | (KL) | 112,5KVA | 112,5KVA | ANCORAR | 112,5KVA | 112,5KVA | 112,5KVA | BT0 | (DCIM) | AVENIDA | (DCIM)</t>
+          <t>(DCIM) | 3 | 4 | BT | AV. | 0 | 3M | 1x3x120(70)AX | 4 | 3 | AV. | 0 | (DCIM) | C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | BT | 3 | CONEX. | 3 | (DCIM) | CONEX.</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -837,27 +841,19 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>P4-7 | CMB | 564661 | ESTR. | YOSHIDA | 175ET005296879 | II | 30M | 44M | S44(2)112,5KVASMPI | AV. | 112,5KVA | B1F | BT | 112,5KVA | 112,5KVA | CONEX. | 30K | (DCIM) | CONEX. | 112,5KVA | 3x336AN | 112,5KVA | C12X600112,5KVACE-SH112,5KVAET4A112,5KVASMTR112,5KVAL1(2)112,5KVAIP | 30K | P5 | Z | (DCIM) | BT | (DCIM) | 30K | 37,5KVA | CONEX. | 112,5KVA | 37,5KVA | 30K | 30K | 30K | 112,5KVA | 112,5KVA | BT | 1x3x120(70)AX | CONEX. | (DCIM) | AVENIDA | B1F | (DCIM) | BT | 112,5KVA | CONEX. | CONEX. | 112,5KVA | 112,5KVA | 112,5KVA | (DCIM) | ANCORAR | ANCORAR | 3x336AN | 112,5KVA | Z | (DCIM) | (DCIM) | 30K | ANCORAR | ESTR. | 46 | CAMINHÃO | 3x336AN | 112,5KVA | 30K | 30K | (KL) | (KL) | (DCIM) | 3x336AN | CAMINHÃO | 37,5KVA | AV. | 30K | 112,5KVA | 112,5KVA | 112,5KVA | 30K | 30K | 30K | 1x3x120(70)AX | CONEX. | ANCORAR | (DCIM) | 112,5KVA | 4x1/0AN | 30K | B1F | 112,5KVA | 30K | 112,5KVA | (DCIM) | 1x2x4AC | BF-A | ANCORAR | 112,5KVA | 112,5KVA | 30K | 112,5KVA | AV. | BT | AV. | (DCIM) | (DCIM) | 30K | _ | 30K | 30K | (DCIM)</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>CMB | 175ET005296879 | 564661 | ESTR. | YOSHIDA | 25.30M | 5 | AV. | 2 | 44M | (DCIM) | 3x336AN | Z</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -898,11 +894,11 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>P8 | C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | (DCIM) | 30K | 1x2x4AC | BT | DIVISA | AV. | N°: | 30K | 1x3x120(70)AX | 3M | 30K | 1x2x4AC | AV. | 1x3x240(120)AX | (DCIM) | 30K | CONEX. | BT | 30K | 30K | 4x1/0AN | (DCIM) | CONEX. | SEM | 30K | 1x3x120(70)AX | PASSEIO | 37,5KVA | NF | 3x336AN | 30K | 30K | 175ET005296879 | Z | 112,5KVA | P31 | (DCIM) | CONEX. | 112,5KVA | ANCORAR | 1x3x120(70)AX | ANCORAR | (DCIM) | (DCIM) | 30K | 112,5KVA | 3x185AX(5AZN) | ANCORAR | CMB | 112,5KVA | 564660 | 112,5KVA | BT0 | CONEX. | 112,5KVA | ESTR. | Z | 112,5KVA | (KL) | 112,5KVA | 112,5KVA | 400816F | CAMINHÃO | 3x336AN | BF-A | CONEX. | 30M | 1x2x4AC | 112,5KVA | 112,5KVA | (DCIM) | P4-7 | 30K | 564661 | 400816F | B1F | 112,5KVA | CONEX. | 112,5KVA | (DCIM) | BT | 112,5KVA | 112,5KVA</t>
+          <t>DIVISA | SEM | C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | PASSEIO | N°: | 40 | 4x1/0AN | 30</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -935,27 +931,19 @@
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>P31 | 564660 | NF | 30K | 1x3x120(70)AX | 1x3x120(70)AX | 30K | CONEX. | 112,5KVA | 30K | 112,5KVA | 30K | CONEX. | (DCIM) | AV. | 30K | 1x2x4AC | CONEX. | 30K | 112,5KVA | 3x185AX(5AZN) | 112,5KVA | CONEX. | Z | BF-A | 3x336AN | 112,5KVA | (DCIM) | 112,5KVA | (DCIM) | 400816F | BT | 30K | 112,5KVA | 30K | P8 | CONEX. | B1F | AV. | C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | 1x2x4AC | 30K | 3M | BT | BT0 | (DCIM) | (KL) | 112,5KVA | CORDOALHA | DIVISA | 112,5KVA | ANCORAR | 30K | (DCIM) | 3x336AN | P1-11 | S44(2)112,5KVASMPI | 1AF(1) | 46 | SEM | (DCIM) | CE2-3LF | B1F | 3x336AN | BT | 112,5KVA | 112,5KVA | (KL) | 112,5KVA | C12X600112,5KVACE4112,5KVABF-A112,5KVASMTG112,5KVAL1(2)112,5KVAIP | N°: | 112,5KVA | (DCIM) | 1AF(1) | (DCIM) | PASSEIO | 1x3x120(70)AX | B1F | BT | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>564660 | NF | (DCIM) | 0 | 1x3x120(70)AX | 1x3x120(70)AX | 0 | CONEX. | 2 | 1 | 3 | CONEX. | 0 | BF-A | 3 | AV. | 4 | CONEX. | 3 | 1 | 3x185AX(5AZN) | 112,5KVA | CONEX.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">

--- a/output_excel/17176206.xlsx
+++ b/output_excel/17176206.xlsx
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -562,27 +580,30 @@
           <t>V5-6</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>30.96m</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>(DCIM) | 3 | (DCIM) | 7 | 7 | AV. | 6 | 1 | 1 | AV. | 112,5KVA | 0 | CAMPO | 0 | 3 | 112,5KVA | 8 | 3 | 0 | BF-A | ANCORAR | 2 | 6 | (DCIM) | 175ET005296879 | (DCIM) | 7 | CONEX. | (DCIM) | 1 | 3x336AN | 0 | 2 | ANCORAR | BF-A | 7 | 2 | 6 | 112,5KVA | (DCIM) | Z | 7 | 1 | (DCIM) | 1 | BT0 | 7 | 112,5KVA | 1x3x120(70)AX | 1 | 5 | 7 | (DCIM) | (DCIM) | 0 | CONEX. | 2 | 112,5KVA | 1 | CABOS | 0 | CONEX. | 4 | 7 | 3 | 4 | CONEX. | (DCIM) | (DCIM) | CONEX. | 2 | 1 | 3 | 1 | 2 | (DCIM)112,5KVA | CONEX. | CABOS | BT | 6 | (KL) | B1F | BT | MT | 1 | (DCIM) | 0 | 112,5KVA | CORDOALHA | (DCIM) | (DCIM) | 1RU6A | B1F | 0 | 1AF(1) | 112,5KVA | (DCIM) | 112,5KVA | 2 | 1RU6A | C12x1000,CE2 | (DCIM) | (KL) | 1RU6A | ANCORAR | 3x70AX(5AZN) | 112,5KVA | 112,5KVA | (DCIM) | 1 | (DCIM) | 4 | (KL) | (DCIM) | 3 | (DCIM) | 112,5KVA | 112,5KVA | BT | CABOS | (DCIM) | 5</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+          <t>30.96m</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>B1F (DCIM) BT BT 1 3 CONEX. CONEX. 3 7 CONEX. 0 1 112,5KVA 2 CONEX. 0 (DCIM) (DCIM) 5 7 112,5KVA 1x3x120(70)AX CRUZ 112,5KVA 1x4ANA | 2 CS's 4 4 (DCIM) 2 (DCIM)112,5KVA2 CS's (DCIM) 1AF(1) (KL) (DCIM) (DCIM) | MT 3x70AX(5AZN) | P6 1 2 1RU6A 1RU6A 112,5KVA 112,5KVA (DCIM) (DCIM) 112,5KVA 112,5KVA (KL) DIVISA BT (KL) 1RU6A (DCIM) BIF | AFASTADOR PROJETO BT0 FERRAGEM | S44(2)112,5KVASMPI (DCIM)</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -607,27 +628,30 @@
           <t>V3-8</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>3m</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>BT | (DCIM) | 3M | 3 | (DCIM) | 4 | AV. | 4 | BT | AV. | 1x3x120(70)AX | 0 | 0 | (DCIM) | 3 | 3 | ANCORAR | 3 | CONEX. | (DCIM) | 7 | 1RU6A | 3x336AN | CONEX. | 112,5KVA | 0 | (DCIM) | 8 | Z | BF-A | 112,5KVA | ANCORAR | 4 | 1x3x120(70)AX | 112,5KVA | CONEX. | BT0 | 112,5KVA | 0 | B1F | BT | (DCIM) | (KL) | 3x185AX(5AZN) | 1 | 5 | CONEX. | 1x3x120(70)AX | CAMINHÃO | 3 | CONEX. | 112,5KVA | CONEX.</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
+          <t>32.96m</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>B1F (DCIM) BT BT 1 3 CONEX. CONEX. 3 7 CONEX. 0 1 112,5KVA 2 CONEX. 0 (DCIM) (DCIM) 5 7 112,5KVA 0 (DCIM) CRUZ 112,5KVA 1x4ANA | 32.96M | B1F BT 0 (DCIM) B1F BT BT 1 3 CONEX. CONEX. 3 7 CONEX. 0 1 112,5KVA 2 CONEX. 0 (DCIM) (DCIM) 5 7 112,5KVA 0 CRUZ 1x3x120(70)AX 1x4ANA | CACHIMBO</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -655,20 +679,31 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | (DCIM) | ANCORAR | BF-A | (DCIM) | (DCIM) | ANCORAR | 8 | BF-A | 3 | 7 | 1 | 3 | 6 | 1 | 7 | (DCIM) | 7 | 0 | 6 | (DCIM) | 2 | 7 | 112,5KVA | 2 | 1 | CAMPO | .7 | 171 | 7 | 112,5KVA | .7 | 4 | 1 | BT | 4 | 1 | AVENIDA | DG | 1 | (DCIM) | B1F | (DCIM) | 3x336AN | CONEX. | 0 | BT | (DCIM) | (DCIM) | BT | Z | 112,5KVA | BT | 112,5KVA | ANCORAR | 1x3x120(70)AX | 1 | 2 | (DCIM) | 112,5KVA | B1F | 3 | (DCIM) | 0 | CONEX. | CORDOALHA | CE2-3LF | YOSHIDA | CONEX. | IP | BF-A | 3x185AX(5AZN) | 3 | 112,5KVA | MT | 1 | 1x3x120(70)AX | (DCIM)112,5KVA | CABOS | CONEX. | 3x185AX(5AZN) | CONEX. | CAMINHÃO | 2 | 8 | 0 | ANCORAR | 1 | (DCIM) | 112,5KVA | (KL) | 5 | 2 | (DCIM) | 1 | 2 | S44(2)112,5KVASMPI | YOSHIDA | 5 | 112,5KVA | 112,5KVA | 1</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE4112,5KVABF-A112,5KVASMTG112,5KVAL1(2)112,5KVAIP B1F 1AF(1) 5 6 46 6 0 2 5 (KL) | (DCIM) | C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | P2 | 2 CS's (DCIM) 1AF(1) (KL)112,5KVA(KL) 1 (DCIM) 2 (DCIM)112,5KVAIP</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -694,30 +729,33 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>S44(2)112,5KVASMPI | (DCIM) | C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | RAMAL | 1 | BIF</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | S44(2)112,5KVASMPI (DCIM) | (DCIM) 3 CS´S | (DCIM) 1 2 CONEX. 6 0 0112,5KVAC12x1000,CE2 4112,5KVA2 CS's (DCIM) | 2 CS's 4 4 (DCIM) 2 (DCIM)112,5KVA2 CS's (DCIM) 1AF(1) (KL) (DCIM) (DCIM) | 1 RAMAL BIF | S44(2)112,5KVASMPI</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -743,30 +781,33 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>S44(2)112,5KVASMPI | C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | 1 | RAMAL | (DCIM) | 5 | 3 | AV. | 3</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | S44(2)112,5KVASMPI (DCIM) | (DCIM) 3 CS´S | S44(2)112,5KVASMPI | 27.63m P5 | 1 RAMAL BIF | (DCIM) 1 2 CONEX. 6 0 0112,5KVAC12x1000,CE2 4112,5KVA2 CS's (DCIM)</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -792,30 +833,33 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>(DCIM) | 3 | 4 | BT | AV. | 0 | 3M | 1x3x120(70)AX | 4 | 3 | AV. | 0 | (DCIM) | C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | BT | 3 | CONEX. | 3 | (DCIM) | CONEX.</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | C12X600112,5KVACE4112,5KVABF-A112,5KVASMTG112,5KVAL1(2)112,5KVAIP B1F 1AF(1) 5 6 46 6 0 2 5 (KL) | xP8 | NF | DIVISA N°: 40 4x1/0AN 30</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -843,20 +887,31 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>CMB | 175ET005296879 | 564661 | ESTR. | YOSHIDA | 25.30M | 5 | AV. | 2 | 44M | (DCIM) | 3x336AN | Z</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | C12X600112,5KVACE2112,5KVASMTG112,5KVAL1(2)112,5KVAIP | S44(2)112,5KVASMPI | P4-7 | 175ET005296879 564661 | C12X600112,5KVACE4112,5KVABF-A112,5KVASMTG112,5KVAL1(2)112,5KVAIP B1F 1AF(1) 5 6 46 6 0 2 5 (KL) | ESTR. YOSHIDA IIx</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -882,30 +937,33 @@
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>DIVISA | SEM | C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | PASSEIO | N°: | 40 | 4x1/0AN | 30</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | C12X600112,5KVACE4112,5KVABF-A112,5KVASMTG112,5KVAL1(2)112,5KVAIP B1F 1AF(1) 5 6 46 6 0 2 5 (KL) | DIVISA N°: 40 4x1/0AN 30 | PASSEIO ESTR. | xP8 | S44(2)112,5KVASMPI</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -933,20 +991,31 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>564660 | NF | (DCIM) | 0 | 1x3x120(70)AX | 1x3x120(70)AX | 0 | CONEX. | 2 | 1 | 3 | CONEX. | 0 | BF-A | 3 | AV. | 4 | CONEX. | 3 | 1 | 3x185AX(5AZN) | 112,5KVA | CONEX.</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVAC12x300,CE1A,S44(2),SMPI112,5KVAS44(2)112,5KVASMPI | C12X600112,5KVACE4112,5KVABF-A112,5KVASMTG112,5KVAL1(2)112,5KVAIP B1F 1AF(1) 5 6 46 6 0 2 5 (KL) | P31 | NF | BF-A 564660 | (DCIM)</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
